--- a/dist/tally_templates/NSFR.xlsx
+++ b/dist/tally_templates/NSFR.xlsx
@@ -1462,7 +1462,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="11">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -3112,7 +3112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="609">
+  <cellXfs count="646">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4918,6 +4918,117 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4926,11 +5037,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5198,7 +5309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6009,7 +6120,7 @@
       <c r="G8" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="299" t="s">
+      <c r="H8" s="643" t="s">
         <v>190</v>
       </c>
       <c r="I8" s="299"/>
@@ -7232,7 +7343,7 @@
       <c r="G51" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="299" t="s">
+      <c r="H51" s="643" t="s">
         <v>190</v>
       </c>
       <c r="I51" s="299"/>
@@ -7357,27 +7468,17 @@
       <c r="Y54" s="5"/>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="366" t="s">
-        <v>200</v>
-      </c>
+      <c r="A55" s="366"/>
       <c r="B55" s="367"/>
-      <c r="C55" s="366" t="s">
-        <v>201</v>
-      </c>
+      <c r="C55" s="366"/>
       <c r="D55" s="368"/>
       <c r="E55" s="368"/>
-      <c r="F55" s="369">
-        <v>-20</v>
-      </c>
-      <c r="G55" s="369">
-        <v>-13.7</v>
-      </c>
+      <c r="F55" s="369"/>
+      <c r="G55" s="369"/>
       <c r="H55" s="370" t="s">
         <v>202</v>
       </c>
-      <c r="I55" s="366" t="s">
-        <v>104</v>
-      </c>
+      <c r="I55" s="366"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
@@ -8449,7 +8550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -9194,7 +9295,7 @@
       <c r="I6" s="151" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="151"/>
+      <c r="J6" s="627"/>
       <c r="K6" s="182" t="str">
         <f>'OS-OUT'!H6</f>
         <v>2615S</v>
@@ -9250,7 +9351,7 @@
       <c r="A8" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="195" t="s">
+      <c r="B8" s="197" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="195"/>
@@ -9311,7 +9412,7 @@
       <c r="X9" s="151"/>
       <c r="Y9" s="151"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="201" t="s">
         <v>11</v>
       </c>
@@ -9352,7 +9453,7 @@
       <c r="X10" s="151"/>
       <c r="Y10" s="151"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="204"/>
       <c r="B11" s="204"/>
       <c r="C11" s="249"/>
@@ -10218,7 +10319,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10515,7 +10616,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -10575,7 +10676,7 @@
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="609" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5"/>
@@ -10584,13 +10685,13 @@
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="610"/>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="611"/>
       <c r="L4" s="14"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
@@ -10637,20 +10738,20 @@
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17"/>
+      <c r="B6" s="610"/>
       <c r="C6" s="5"/>
       <c r="D6" s="11"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="610"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="19"/>
+      <c r="K6" s="612"/>
       <c r="L6" s="20" t="s">
         <v>9</v>
       </c>
@@ -11777,7 +11878,7 @@
       <c r="Y43" s="42"/>
     </row>
     <row r="44" ht="16.9" customHeight="1" hidden="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
+      <c r="A44" s="613"/>
       <c r="B44" s="87"/>
       <c r="C44" s="88" t="s">
         <v>18</v>
@@ -11806,7 +11907,7 @@
       <c r="Y44" s="42"/>
     </row>
     <row r="45" ht="16.9" customHeight="1" hidden="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="89"/>
+      <c r="A45" s="614"/>
       <c r="B45" s="90"/>
       <c r="C45" s="91" t="s">
         <v>19</v>
@@ -12961,7 +13062,7 @@
       <c r="X84" s="5"/>
       <c r="Y84" s="5"/>
     </row>
-    <row r="85" ht="13.5" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="14.9" customHeight="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="128" t="s">
         <v>21</v>
       </c>
@@ -13466,7 +13567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -14121,7 +14222,7 @@
       <c r="A6" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="B6" s="42"/>
+      <c r="B6" s="644"/>
       <c r="C6" s="42"/>
       <c r="D6" s="242" t="str">
         <f>'Final Work'!B4</f>
@@ -14140,7 +14241,7 @@
       <c r="O6" s="242" t="s">
         <v>188</v>
       </c>
-      <c r="P6" s="42"/>
+      <c r="P6" s="644"/>
       <c r="Q6" s="42"/>
       <c r="R6" s="189" t="str">
         <f>'Final Work'!G4</f>
@@ -14210,7 +14311,7 @@
       <c r="A8" s="149" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="149"/>
+      <c r="B8" s="645"/>
       <c r="C8" s="149"/>
       <c r="D8" s="421" t="s">
         <v>213</v>
@@ -14228,7 +14329,7 @@
       <c r="O8" s="421" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="149"/>
+      <c r="P8" s="645"/>
       <c r="Q8" s="149"/>
       <c r="R8" s="420">
         <f>'Final Work'!G6</f>
@@ -14245,7 +14346,7 @@
       </c>
       <c r="Z8" s="420"/>
       <c r="AA8" s="420"/>
-      <c r="AB8" s="420" t="s">
+      <c r="AB8" s="645" t="s">
         <v>26</v>
       </c>
       <c r="AC8" s="420"/>
@@ -16916,7 +17017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -17722,13 +17823,13 @@
       <c r="G6" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="182"/>
+      <c r="H6" s="197"/>
       <c r="I6" s="182"/>
       <c r="J6" s="151"/>
       <c r="K6" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="196"/>
+      <c r="L6" s="626"/>
       <c r="M6" s="182"/>
       <c r="N6" s="5"/>
       <c r="O6" s="151"/>
@@ -17774,7 +17875,7 @@
       <c r="A8" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="627" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="151"/>
@@ -17784,13 +17885,13 @@
       <c r="G8" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="182"/>
+      <c r="H8" s="197"/>
       <c r="I8" s="182"/>
       <c r="J8" s="151"/>
       <c r="K8" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="198"/>
+      <c r="L8" s="197"/>
       <c r="M8" s="151"/>
       <c r="N8" s="151"/>
       <c r="O8" s="151"/>
@@ -17907,19 +18008,19 @@
       <c r="Y11" s="151"/>
     </row>
     <row r="12" ht="24.95" customHeight="1" hidden="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="628"/>
       <c r="B12" s="206"/>
       <c r="C12" s="207"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="209"/>
-      <c r="F12" s="210"/>
+      <c r="D12" s="629"/>
+      <c r="E12" s="630"/>
+      <c r="F12" s="631"/>
       <c r="G12" s="211"/>
       <c r="H12" s="212"/>
       <c r="I12" s="213"/>
       <c r="J12" s="214"/>
       <c r="K12" s="211"/>
       <c r="L12" s="211"/>
-      <c r="M12" s="215"/>
+      <c r="M12" s="340"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
@@ -17934,19 +18035,19 @@
       <c r="Y12" s="10"/>
     </row>
     <row r="13" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
+      <c r="A13" s="628"/>
       <c r="B13" s="206"/>
       <c r="C13" s="207"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="209"/>
-      <c r="F13" s="210"/>
+      <c r="D13" s="629"/>
+      <c r="E13" s="630"/>
+      <c r="F13" s="631"/>
       <c r="G13" s="211"/>
       <c r="H13" s="212"/>
       <c r="I13" s="213"/>
       <c r="J13" s="214"/>
       <c r="K13" s="211"/>
       <c r="L13" s="211"/>
-      <c r="M13" s="215"/>
+      <c r="M13" s="340"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
@@ -17961,19 +18062,19 @@
       <c r="Y13" s="10"/>
     </row>
     <row r="14" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="216"/>
+      <c r="A14" s="632"/>
       <c r="B14" s="200"/>
       <c r="C14" s="200"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="218"/>
-      <c r="F14" s="219"/>
+      <c r="D14" s="633"/>
+      <c r="E14" s="634"/>
+      <c r="F14" s="635"/>
       <c r="G14" s="200"/>
       <c r="H14" s="220"/>
       <c r="I14" s="221"/>
       <c r="J14" s="220"/>
       <c r="K14" s="200"/>
       <c r="L14" s="200"/>
-      <c r="M14" s="216"/>
+      <c r="M14" s="632"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -17988,19 +18089,19 @@
       <c r="Y14" s="10"/>
     </row>
     <row r="15" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="216"/>
+      <c r="A15" s="632"/>
       <c r="B15" s="200"/>
       <c r="C15" s="200"/>
-      <c r="D15" s="217"/>
-      <c r="E15" s="218"/>
-      <c r="F15" s="219"/>
+      <c r="D15" s="633"/>
+      <c r="E15" s="634"/>
+      <c r="F15" s="635"/>
       <c r="G15" s="200"/>
       <c r="H15" s="220"/>
       <c r="I15" s="221"/>
       <c r="J15" s="220"/>
       <c r="K15" s="200"/>
       <c r="L15" s="200"/>
-      <c r="M15" s="222"/>
+      <c r="M15" s="321"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -18015,19 +18116,19 @@
       <c r="Y15" s="10"/>
     </row>
     <row r="16" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="216"/>
+      <c r="A16" s="632"/>
       <c r="B16" s="200"/>
       <c r="C16" s="200"/>
-      <c r="D16" s="217"/>
-      <c r="E16" s="218"/>
-      <c r="F16" s="219"/>
+      <c r="D16" s="633"/>
+      <c r="E16" s="634"/>
+      <c r="F16" s="635"/>
       <c r="G16" s="200"/>
       <c r="H16" s="220"/>
       <c r="I16" s="221"/>
       <c r="J16" s="220"/>
       <c r="K16" s="200"/>
       <c r="L16" s="200"/>
-      <c r="M16" s="216"/>
+      <c r="M16" s="632"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
@@ -18042,19 +18143,19 @@
       <c r="Y16" s="10"/>
     </row>
     <row r="17" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="216"/>
+      <c r="A17" s="632"/>
       <c r="B17" s="200"/>
       <c r="C17" s="200"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="218"/>
-      <c r="F17" s="219"/>
+      <c r="D17" s="636"/>
+      <c r="E17" s="634"/>
+      <c r="F17" s="635"/>
       <c r="G17" s="200"/>
       <c r="H17" s="220"/>
       <c r="I17" s="221"/>
       <c r="J17" s="220"/>
       <c r="K17" s="200"/>
       <c r="L17" s="200"/>
-      <c r="M17" s="216"/>
+      <c r="M17" s="632"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
@@ -18069,19 +18170,19 @@
       <c r="Y17" s="10"/>
     </row>
     <row r="18" ht="24.95" customHeight="1" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="216"/>
+      <c r="A18" s="632"/>
       <c r="B18" s="200"/>
       <c r="C18" s="200"/>
-      <c r="D18" s="217"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="219"/>
+      <c r="D18" s="633"/>
+      <c r="E18" s="634"/>
+      <c r="F18" s="635"/>
       <c r="G18" s="200"/>
       <c r="H18" s="220"/>
       <c r="I18" s="221"/>
       <c r="J18" s="220"/>
       <c r="K18" s="200"/>
       <c r="L18" s="200"/>
-      <c r="M18" s="216"/>
+      <c r="M18" s="632"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
@@ -18730,7 +18831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -19473,7 +19574,7 @@
       <c r="I6" s="151" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="151"/>
+      <c r="J6" s="627"/>
       <c r="K6" s="182" t="str">
         <f>'OS-IN'!H6</f>
         <v>2614N</v>
@@ -19529,7 +19630,7 @@
       <c r="A8" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="195" t="s">
+      <c r="B8" s="197" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="195"/>
@@ -19590,7 +19691,7 @@
       <c r="X9" s="151"/>
       <c r="Y9" s="151"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="199" t="s">
         <v>11</v>
       </c>
@@ -19631,7 +19732,7 @@
       <c r="X10" s="151"/>
       <c r="Y10" s="151"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="202"/>
       <c r="B11" s="202"/>
       <c r="C11" s="249"/>
@@ -20500,7 +20601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="12" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7.5" customHeight="1"/>
   <cols>
@@ -22085,39 +22186,17 @@
       <c r="Y7" s="568"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="603">
-        <v>1</v>
-      </c>
-      <c r="B8" s="604" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="605" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="606" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="607">
-        <v>29.6</v>
-      </c>
-      <c r="F8" s="605" t="s">
-        <v>260</v>
-      </c>
-      <c r="G8" s="605">
-        <v>240786</v>
-      </c>
-      <c r="H8" s="604" t="s">
-        <v>261</v>
-      </c>
-      <c r="I8" s="608" t="s">
-        <v>262</v>
-      </c>
-      <c r="J8" s="605" t="s">
-        <v>263</v>
-      </c>
-      <c r="K8" s="605" t="s">
-        <v>264</v>
-      </c>
+      <c r="A8" s="603"/>
+      <c r="B8" s="604"/>
+      <c r="C8" s="605"/>
+      <c r="D8" s="606"/>
+      <c r="E8" s="607"/>
+      <c r="F8" s="605"/>
+      <c r="G8" s="605"/>
+      <c r="H8" s="604"/>
+      <c r="I8" s="608"/>
+      <c r="J8" s="605"/>
+      <c r="K8" s="605"/>
       <c r="L8" s="605"/>
       <c r="M8" s="605"/>
       <c r="N8" s="605"/>
@@ -22438,7 +22517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -23144,7 +23223,7 @@
       <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="154" t="s">
+      <c r="B7" s="615" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="156"/>
@@ -23159,7 +23238,7 @@
       <c r="G7" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="616" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="10"/>
@@ -23299,7 +23378,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="50"/>
-      <c r="C12" s="163"/>
+      <c r="C12" s="617"/>
       <c r="D12" s="163"/>
       <c r="E12" s="163"/>
       <c r="F12" s="163"/>
@@ -23326,7 +23405,7 @@
     <row r="13" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="164"/>
       <c r="B13" s="165"/>
-      <c r="C13" s="166"/>
+      <c r="C13" s="618"/>
       <c r="D13" s="166"/>
       <c r="E13" s="166"/>
       <c r="F13" s="166"/>
@@ -23353,7 +23432,7 @@
     <row r="14" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="164"/>
       <c r="B14" s="68"/>
-      <c r="C14" s="167"/>
+      <c r="C14" s="619"/>
       <c r="D14" s="168"/>
       <c r="E14" s="168"/>
       <c r="F14" s="168"/>
@@ -23382,7 +23461,7 @@
     <row r="15" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="164"/>
       <c r="B15" s="58"/>
-      <c r="C15" s="170"/>
+      <c r="C15" s="620"/>
       <c r="D15" s="171"/>
       <c r="E15" s="171"/>
       <c r="F15" s="171"/>
@@ -23409,7 +23488,7 @@
     <row r="16" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="77"/>
       <c r="B16" s="76"/>
-      <c r="C16" s="173"/>
+      <c r="C16" s="621"/>
       <c r="D16" s="174"/>
       <c r="E16" s="174"/>
       <c r="F16" s="174"/>
@@ -23438,7 +23517,7 @@
     <row r="17" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="176"/>
       <c r="B17" s="68"/>
-      <c r="C17" s="167"/>
+      <c r="C17" s="619"/>
       <c r="D17" s="168"/>
       <c r="E17" s="168"/>
       <c r="F17" s="168"/>
@@ -23467,7 +23546,7 @@
     <row r="18" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="177"/>
       <c r="B18" s="178"/>
-      <c r="C18" s="167"/>
+      <c r="C18" s="619"/>
       <c r="D18" s="168"/>
       <c r="E18" s="168"/>
       <c r="F18" s="168"/>
@@ -23494,7 +23573,7 @@
     <row r="19" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="164"/>
       <c r="B19" s="68"/>
-      <c r="C19" s="167"/>
+      <c r="C19" s="619"/>
       <c r="D19" s="168"/>
       <c r="E19" s="168"/>
       <c r="F19" s="168"/>
@@ -23521,7 +23600,7 @@
     <row r="20" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="179"/>
       <c r="B20" s="178"/>
-      <c r="C20" s="167"/>
+      <c r="C20" s="619"/>
       <c r="D20" s="168"/>
       <c r="E20" s="168"/>
       <c r="F20" s="168"/>
@@ -23548,7 +23627,7 @@
     <row r="21" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="180"/>
       <c r="B21" s="76"/>
-      <c r="C21" s="173"/>
+      <c r="C21" s="621"/>
       <c r="D21" s="174"/>
       <c r="E21" s="174"/>
       <c r="F21" s="174"/>
@@ -23577,7 +23656,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="68"/>
-      <c r="C22" s="167"/>
+      <c r="C22" s="619"/>
       <c r="D22" s="168"/>
       <c r="E22" s="168"/>
       <c r="F22" s="168"/>
@@ -23604,7 +23683,7 @@
     <row r="23" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="69"/>
       <c r="B23" s="68"/>
-      <c r="C23" s="167"/>
+      <c r="C23" s="619"/>
       <c r="D23" s="168"/>
       <c r="E23" s="168"/>
       <c r="F23" s="168"/>
@@ -23631,7 +23710,7 @@
     <row r="24" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="164"/>
       <c r="B24" s="68"/>
-      <c r="C24" s="183"/>
+      <c r="C24" s="622"/>
       <c r="D24" s="183"/>
       <c r="E24" s="183"/>
       <c r="F24" s="183"/>
@@ -23658,7 +23737,7 @@
     <row r="25" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="108"/>
       <c r="B25" s="178"/>
-      <c r="C25" s="170"/>
+      <c r="C25" s="620"/>
       <c r="D25" s="171"/>
       <c r="E25" s="171"/>
       <c r="F25" s="171"/>
@@ -23685,7 +23764,7 @@
     <row r="26" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="77"/>
       <c r="B26" s="178"/>
-      <c r="C26" s="173"/>
+      <c r="C26" s="621"/>
       <c r="D26" s="174"/>
       <c r="E26" s="174"/>
       <c r="F26" s="174"/>
@@ -23712,7 +23791,7 @@
     <row r="27" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31"/>
       <c r="B27" s="29"/>
-      <c r="C27" s="167"/>
+      <c r="C27" s="619"/>
       <c r="D27" s="168"/>
       <c r="E27" s="168"/>
       <c r="F27" s="168"/>
@@ -23739,7 +23818,7 @@
     <row r="28" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="164"/>
       <c r="B28" s="68"/>
-      <c r="C28" s="167"/>
+      <c r="C28" s="619"/>
       <c r="D28" s="168"/>
       <c r="E28" s="168"/>
       <c r="F28" s="168"/>
@@ -23766,7 +23845,7 @@
     <row r="29" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="164"/>
       <c r="B29" s="58"/>
-      <c r="C29" s="170"/>
+      <c r="C29" s="620"/>
       <c r="D29" s="171"/>
       <c r="E29" s="171"/>
       <c r="F29" s="171"/>
@@ -23791,9 +23870,9 @@
       <c r="Y29" s="151"/>
     </row>
     <row r="30" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="184"/>
+      <c r="A30" s="623"/>
       <c r="B30" s="178"/>
-      <c r="C30" s="167"/>
+      <c r="C30" s="619"/>
       <c r="D30" s="168"/>
       <c r="E30" s="168"/>
       <c r="F30" s="168"/>
@@ -23818,9 +23897,9 @@
       <c r="Y30" s="151"/>
     </row>
     <row r="31" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="185"/>
+      <c r="A31" s="624"/>
       <c r="B31" s="76"/>
-      <c r="C31" s="173"/>
+      <c r="C31" s="621"/>
       <c r="D31" s="174"/>
       <c r="E31" s="174"/>
       <c r="F31" s="174"/>
@@ -23847,7 +23926,7 @@
     <row r="32" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="31"/>
       <c r="B32" s="68"/>
-      <c r="C32" s="186"/>
+      <c r="C32" s="625"/>
       <c r="D32" s="187"/>
       <c r="E32" s="187"/>
       <c r="F32" s="187"/>
@@ -23874,7 +23953,7 @@
     <row r="33" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="164"/>
       <c r="B33" s="68"/>
-      <c r="C33" s="167"/>
+      <c r="C33" s="619"/>
       <c r="D33" s="168"/>
       <c r="E33" s="168"/>
       <c r="F33" s="168"/>
@@ -23899,9 +23978,9 @@
       <c r="Y33" s="151"/>
     </row>
     <row r="34" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="184"/>
+      <c r="A34" s="623"/>
       <c r="B34" s="58"/>
-      <c r="C34" s="170"/>
+      <c r="C34" s="620"/>
       <c r="D34" s="171"/>
       <c r="E34" s="171"/>
       <c r="F34" s="171"/>
@@ -23926,9 +24005,9 @@
       <c r="Y34" s="151"/>
     </row>
     <row r="35" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="184"/>
+      <c r="A35" s="623"/>
       <c r="B35" s="68"/>
-      <c r="C35" s="183"/>
+      <c r="C35" s="622"/>
       <c r="D35" s="183"/>
       <c r="E35" s="183"/>
       <c r="F35" s="183"/>
@@ -23953,9 +24032,9 @@
       <c r="Y35" s="151"/>
     </row>
     <row r="36" ht="19.9" customHeight="1" spans="1:25" s="151" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="185"/>
+      <c r="A36" s="624"/>
       <c r="B36" s="68"/>
-      <c r="C36" s="183"/>
+      <c r="C36" s="622"/>
       <c r="D36" s="183"/>
       <c r="E36" s="183"/>
       <c r="F36" s="183"/>
@@ -24252,7 +24331,7 @@
       <c r="Y46" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -24286,6 +24365,9 @@
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.31496062992125984" footer="0.35433070866141736"/>
@@ -24294,7 +24376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -25099,13 +25181,13 @@
       <c r="G6" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="182"/>
+      <c r="H6" s="197"/>
       <c r="I6" s="182"/>
       <c r="J6" s="151"/>
       <c r="K6" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="196"/>
+      <c r="L6" s="626"/>
       <c r="M6" s="182"/>
       <c r="N6" s="5"/>
       <c r="O6" s="151"/>
@@ -25151,7 +25233,7 @@
       <c r="A8" s="195" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="627" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="258"/>
@@ -25161,13 +25243,13 @@
       <c r="G8" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="182"/>
+      <c r="H8" s="197"/>
       <c r="I8" s="182"/>
       <c r="J8" s="151"/>
       <c r="K8" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="198"/>
+      <c r="L8" s="197"/>
       <c r="M8" s="151"/>
       <c r="N8" s="151"/>
       <c r="O8" s="151"/>
@@ -25209,7 +25291,7 @@
       <c r="X9" s="151"/>
       <c r="Y9" s="151"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="259" t="s">
         <v>49</v>
       </c>
@@ -25254,7 +25336,7 @@
       <c r="X10" s="151"/>
       <c r="Y10" s="151"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="202"/>
       <c r="B11" s="37"/>
       <c r="C11" s="37"/>
@@ -25284,19 +25366,19 @@
       <c r="Y11" s="151"/>
     </row>
     <row r="12" ht="30" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="216"/>
+      <c r="A12" s="632"/>
       <c r="B12" s="200"/>
       <c r="C12" s="200"/>
-      <c r="D12" s="217"/>
-      <c r="E12" s="218"/>
-      <c r="F12" s="219"/>
+      <c r="D12" s="633"/>
+      <c r="E12" s="634"/>
+      <c r="F12" s="635"/>
       <c r="G12" s="200"/>
       <c r="H12" s="220"/>
       <c r="I12" s="221"/>
       <c r="J12" s="220"/>
       <c r="K12" s="200"/>
       <c r="L12" s="200"/>
-      <c r="M12" s="261"/>
+      <c r="M12" s="637"/>
       <c r="N12" s="151"/>
       <c r="O12" s="151"/>
       <c r="P12" s="151"/>
@@ -25311,19 +25393,19 @@
       <c r="Y12" s="151"/>
     </row>
     <row r="13" ht="30" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="216"/>
+      <c r="A13" s="632"/>
       <c r="B13" s="200"/>
       <c r="C13" s="200"/>
-      <c r="D13" s="217"/>
-      <c r="E13" s="218"/>
-      <c r="F13" s="219"/>
+      <c r="D13" s="633"/>
+      <c r="E13" s="634"/>
+      <c r="F13" s="635"/>
       <c r="G13" s="200"/>
       <c r="H13" s="220"/>
       <c r="I13" s="221"/>
       <c r="J13" s="220"/>
       <c r="K13" s="200"/>
       <c r="L13" s="200"/>
-      <c r="M13" s="261"/>
+      <c r="M13" s="637"/>
       <c r="N13" s="151"/>
       <c r="O13" s="151"/>
       <c r="P13" s="151"/>
@@ -25338,19 +25420,19 @@
       <c r="Y13" s="151"/>
     </row>
     <row r="14" ht="30" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="262"/>
+      <c r="A14" s="638"/>
       <c r="B14" s="199"/>
       <c r="C14" s="199"/>
-      <c r="D14" s="263"/>
-      <c r="E14" s="264"/>
-      <c r="F14" s="265"/>
+      <c r="D14" s="639"/>
+      <c r="E14" s="640"/>
+      <c r="F14" s="641"/>
       <c r="G14" s="199"/>
       <c r="H14" s="266"/>
       <c r="I14" s="267"/>
       <c r="J14" s="266"/>
       <c r="K14" s="199"/>
       <c r="L14" s="199"/>
-      <c r="M14" s="268"/>
+      <c r="M14" s="199"/>
       <c r="N14" s="151"/>
       <c r="O14" s="151"/>
       <c r="P14" s="151"/>
@@ -25365,19 +25447,19 @@
       <c r="Y14" s="151"/>
     </row>
     <row r="15" ht="30" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="262"/>
+      <c r="A15" s="638"/>
       <c r="B15" s="199"/>
       <c r="C15" s="199"/>
-      <c r="D15" s="263"/>
-      <c r="E15" s="264"/>
-      <c r="F15" s="265"/>
+      <c r="D15" s="639"/>
+      <c r="E15" s="640"/>
+      <c r="F15" s="641"/>
       <c r="G15" s="199"/>
       <c r="H15" s="266"/>
       <c r="I15" s="267"/>
       <c r="J15" s="266"/>
       <c r="K15" s="199"/>
       <c r="L15" s="199"/>
-      <c r="M15" s="268"/>
+      <c r="M15" s="199"/>
       <c r="N15" s="151"/>
       <c r="O15" s="151"/>
       <c r="P15" s="151"/>
@@ -25392,19 +25474,19 @@
       <c r="Y15" s="151"/>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="262"/>
+      <c r="A16" s="638"/>
       <c r="B16" s="199"/>
       <c r="C16" s="199"/>
-      <c r="D16" s="263"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="265"/>
+      <c r="D16" s="639"/>
+      <c r="E16" s="640"/>
+      <c r="F16" s="641"/>
       <c r="G16" s="199"/>
       <c r="H16" s="266"/>
       <c r="I16" s="267"/>
       <c r="J16" s="266"/>
       <c r="K16" s="199"/>
       <c r="L16" s="199"/>
-      <c r="M16" s="268"/>
+      <c r="M16" s="199"/>
       <c r="N16" s="151"/>
       <c r="O16" s="151"/>
       <c r="P16" s="151"/>
@@ -25419,19 +25501,19 @@
       <c r="Y16" s="151"/>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="262"/>
+      <c r="A17" s="638"/>
       <c r="B17" s="199"/>
       <c r="C17" s="199"/>
-      <c r="D17" s="263"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="265"/>
+      <c r="D17" s="639"/>
+      <c r="E17" s="640"/>
+      <c r="F17" s="641"/>
       <c r="G17" s="199"/>
       <c r="H17" s="266"/>
       <c r="I17" s="267"/>
       <c r="J17" s="266"/>
       <c r="K17" s="199"/>
       <c r="L17" s="199"/>
-      <c r="M17" s="268"/>
+      <c r="M17" s="199"/>
       <c r="N17" s="151"/>
       <c r="O17" s="151"/>
       <c r="P17" s="151"/>
@@ -25446,19 +25528,19 @@
       <c r="Y17" s="151"/>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="262"/>
+      <c r="A18" s="638"/>
       <c r="B18" s="199"/>
       <c r="C18" s="199"/>
-      <c r="D18" s="263"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="265"/>
+      <c r="D18" s="639"/>
+      <c r="E18" s="640"/>
+      <c r="F18" s="641"/>
       <c r="G18" s="199"/>
       <c r="H18" s="266"/>
       <c r="I18" s="267"/>
       <c r="J18" s="266"/>
       <c r="K18" s="199"/>
       <c r="L18" s="199"/>
-      <c r="M18" s="268"/>
+      <c r="M18" s="199"/>
       <c r="N18" s="151"/>
       <c r="O18" s="151"/>
       <c r="P18" s="151"/>
@@ -25473,19 +25555,19 @@
       <c r="Y18" s="151"/>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="262"/>
+      <c r="A19" s="638"/>
       <c r="B19" s="199"/>
       <c r="C19" s="199"/>
-      <c r="D19" s="263"/>
-      <c r="E19" s="264"/>
-      <c r="F19" s="265"/>
+      <c r="D19" s="639"/>
+      <c r="E19" s="640"/>
+      <c r="F19" s="641"/>
       <c r="G19" s="199"/>
       <c r="H19" s="266"/>
       <c r="I19" s="267"/>
       <c r="J19" s="266"/>
       <c r="K19" s="199"/>
       <c r="L19" s="199"/>
-      <c r="M19" s="268"/>
+      <c r="M19" s="199"/>
       <c r="N19" s="151"/>
       <c r="O19" s="151"/>
       <c r="P19" s="151"/>
@@ -26164,7 +26246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26844,7 +26926,7 @@
       <c r="F4" s="292" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="196"/>
+      <c r="G4" s="626"/>
       <c r="H4" s="182"/>
       <c r="I4" s="151"/>
       <c r="J4" s="151"/>
@@ -26904,7 +26986,7 @@
       <c r="F6" s="292" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="291" t="s">
+      <c r="G6" s="642" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="151"/>
@@ -27968,7 +28050,7 @@
       <c r="F43" s="292" t="s">
         <v>85</v>
       </c>
-      <c r="G43" s="291" t="s">
+      <c r="G43" s="642" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="151"/>
@@ -28150,24 +28232,14 @@
       <c r="Y48" s="294"/>
     </row>
     <row r="49" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="313" t="s">
-        <v>101</v>
-      </c>
+      <c r="A49" s="313"/>
       <c r="B49" s="314"/>
-      <c r="C49" s="315" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="315" t="s">
-        <v>15</v>
-      </c>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
       <c r="E49" s="315"/>
-      <c r="F49" s="316" t="s">
-        <v>103</v>
-      </c>
+      <c r="F49" s="316"/>
       <c r="G49" s="315"/>
-      <c r="H49" s="317" t="s">
-        <v>104</v>
-      </c>
+      <c r="H49" s="317"/>
       <c r="I49" s="294"/>
       <c r="J49" s="294"/>
       <c r="K49" s="294"/>
@@ -28187,24 +28259,14 @@
       <c r="Y49" s="294"/>
     </row>
     <row r="50" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="318" t="s">
-        <v>105</v>
-      </c>
+      <c r="A50" s="318"/>
       <c r="B50" s="319"/>
-      <c r="C50" s="320" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C50" s="320"/>
+      <c r="D50" s="322"/>
       <c r="E50" s="322"/>
-      <c r="F50" s="323" t="s">
-        <v>107</v>
-      </c>
+      <c r="F50" s="323"/>
       <c r="G50" s="322"/>
-      <c r="H50" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H50" s="324"/>
       <c r="I50" s="294"/>
       <c r="J50" s="294"/>
       <c r="K50" s="294"/>
@@ -28224,24 +28286,14 @@
       <c r="Y50" s="294"/>
     </row>
     <row r="51" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="325" t="s">
-        <v>108</v>
-      </c>
+      <c r="A51" s="325"/>
       <c r="B51" s="326"/>
-      <c r="C51" s="320" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C51" s="320"/>
+      <c r="D51" s="322"/>
       <c r="E51" s="322"/>
-      <c r="F51" s="323" t="s">
-        <v>110</v>
-      </c>
+      <c r="F51" s="323"/>
       <c r="G51" s="322"/>
-      <c r="H51" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H51" s="324"/>
       <c r="I51" s="294"/>
       <c r="J51" s="294"/>
       <c r="K51" s="294"/>
@@ -28261,24 +28313,14 @@
       <c r="Y51" s="294"/>
     </row>
     <row r="52" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="327" t="s">
-        <v>111</v>
-      </c>
+      <c r="A52" s="327"/>
       <c r="B52" s="358"/>
-      <c r="C52" s="329" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C52" s="329"/>
+      <c r="D52" s="322"/>
       <c r="E52" s="322"/>
-      <c r="F52" s="323" t="s">
-        <v>113</v>
-      </c>
+      <c r="F52" s="323"/>
       <c r="G52" s="322"/>
-      <c r="H52" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H52" s="324"/>
       <c r="I52" s="294"/>
       <c r="J52" s="294"/>
       <c r="K52" s="294"/>
@@ -28298,24 +28340,14 @@
       <c r="Y52" s="294"/>
     </row>
     <row r="53" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="330" t="s">
-        <v>115</v>
-      </c>
+      <c r="A53" s="330"/>
       <c r="B53" s="332"/>
-      <c r="C53" s="332" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="334" t="s">
-        <v>15</v>
-      </c>
+      <c r="C53" s="332"/>
+      <c r="D53" s="334"/>
       <c r="E53" s="334"/>
-      <c r="F53" s="335" t="s">
-        <v>117</v>
-      </c>
+      <c r="F53" s="335"/>
       <c r="G53" s="334"/>
-      <c r="H53" s="359" t="s">
-        <v>104</v>
-      </c>
+      <c r="H53" s="359"/>
       <c r="I53" s="294"/>
       <c r="J53" s="294"/>
       <c r="K53" s="294"/>
@@ -28335,24 +28367,14 @@
       <c r="Y53" s="294"/>
     </row>
     <row r="54" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="337" t="s">
-        <v>118</v>
-      </c>
+      <c r="A54" s="337"/>
       <c r="B54" s="339"/>
-      <c r="C54" s="339" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" s="341" t="s">
-        <v>15</v>
-      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="341"/>
       <c r="E54" s="341"/>
-      <c r="F54" s="342" t="s">
-        <v>120</v>
-      </c>
+      <c r="F54" s="342"/>
       <c r="G54" s="341"/>
-      <c r="H54" s="354" t="s">
-        <v>104</v>
-      </c>
+      <c r="H54" s="354"/>
       <c r="I54" s="294"/>
       <c r="J54" s="294"/>
       <c r="K54" s="294"/>
@@ -28372,24 +28394,14 @@
       <c r="Y54" s="294"/>
     </row>
     <row r="55" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="344" t="s">
-        <v>121</v>
-      </c>
+      <c r="A55" s="344"/>
       <c r="B55" s="329"/>
-      <c r="C55" s="329" t="s">
-        <v>122</v>
-      </c>
-      <c r="D55" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C55" s="329"/>
+      <c r="D55" s="322"/>
       <c r="E55" s="322"/>
-      <c r="F55" s="323" t="s">
-        <v>123</v>
-      </c>
+      <c r="F55" s="323"/>
       <c r="G55" s="322"/>
-      <c r="H55" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H55" s="324"/>
       <c r="I55" s="294"/>
       <c r="J55" s="294"/>
       <c r="K55" s="294"/>
@@ -28409,24 +28421,14 @@
       <c r="Y55" s="294"/>
     </row>
     <row r="56" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="344" t="s">
-        <v>124</v>
-      </c>
+      <c r="A56" s="344"/>
       <c r="B56" s="329"/>
-      <c r="C56" s="329" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C56" s="329"/>
+      <c r="D56" s="322"/>
       <c r="E56" s="322"/>
-      <c r="F56" s="323" t="s">
-        <v>126</v>
-      </c>
+      <c r="F56" s="323"/>
       <c r="G56" s="322"/>
-      <c r="H56" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H56" s="324"/>
       <c r="I56" s="294"/>
       <c r="J56" s="294"/>
       <c r="K56" s="294"/>
@@ -28446,24 +28448,14 @@
       <c r="Y56" s="294"/>
     </row>
     <row r="57" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="346" t="s">
-        <v>127</v>
-      </c>
+      <c r="A57" s="346"/>
       <c r="B57" s="322"/>
-      <c r="C57" s="320" t="s">
-        <v>128</v>
-      </c>
-      <c r="D57" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C57" s="320"/>
+      <c r="D57" s="322"/>
       <c r="E57" s="322"/>
-      <c r="F57" s="320" t="s">
-        <v>129</v>
-      </c>
+      <c r="F57" s="320"/>
       <c r="G57" s="322"/>
-      <c r="H57" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H57" s="324"/>
       <c r="I57" s="294"/>
       <c r="J57" s="294"/>
       <c r="K57" s="294"/>
@@ -28483,24 +28475,14 @@
       <c r="Y57" s="294"/>
     </row>
     <row r="58" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="347" t="s">
-        <v>130</v>
-      </c>
+      <c r="A58" s="347"/>
       <c r="B58" s="333"/>
-      <c r="C58" s="348" t="s">
-        <v>131</v>
-      </c>
-      <c r="D58" s="334" t="s">
-        <v>15</v>
-      </c>
+      <c r="C58" s="348"/>
+      <c r="D58" s="334"/>
       <c r="E58" s="333"/>
-      <c r="F58" s="348" t="s">
-        <v>132</v>
-      </c>
+      <c r="F58" s="348"/>
       <c r="G58" s="333"/>
-      <c r="H58" s="336" t="s">
-        <v>104</v>
-      </c>
+      <c r="H58" s="336"/>
       <c r="I58" s="294"/>
       <c r="J58" s="294"/>
       <c r="K58" s="294"/>
@@ -28520,24 +28502,14 @@
       <c r="Y58" s="294"/>
     </row>
     <row r="59" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="352" t="s">
-        <v>133</v>
-      </c>
+      <c r="A59" s="352"/>
       <c r="B59" s="341"/>
-      <c r="C59" s="353" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" s="341" t="s">
-        <v>15</v>
-      </c>
+      <c r="C59" s="353"/>
+      <c r="D59" s="341"/>
       <c r="E59" s="341"/>
-      <c r="F59" s="353" t="s">
-        <v>135</v>
-      </c>
+      <c r="F59" s="353"/>
       <c r="G59" s="341"/>
-      <c r="H59" s="354" t="s">
-        <v>104</v>
-      </c>
+      <c r="H59" s="354"/>
       <c r="I59" s="294"/>
       <c r="J59" s="294"/>
       <c r="K59" s="294"/>
@@ -28557,24 +28529,14 @@
       <c r="Y59" s="294"/>
     </row>
     <row r="60" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="346" t="s">
-        <v>136</v>
-      </c>
+      <c r="A60" s="346"/>
       <c r="B60" s="322"/>
-      <c r="C60" s="320" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C60" s="320"/>
+      <c r="D60" s="322"/>
       <c r="E60" s="322"/>
-      <c r="F60" s="320" t="s">
-        <v>138</v>
-      </c>
+      <c r="F60" s="320"/>
       <c r="G60" s="322"/>
-      <c r="H60" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H60" s="324"/>
       <c r="I60" s="294"/>
       <c r="J60" s="294"/>
       <c r="K60" s="294"/>
@@ -28594,24 +28556,14 @@
       <c r="Y60" s="294"/>
     </row>
     <row r="61" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="346" t="s">
-        <v>139</v>
-      </c>
+      <c r="A61" s="346"/>
       <c r="B61" s="322"/>
-      <c r="C61" s="320" t="s">
-        <v>140</v>
-      </c>
-      <c r="D61" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C61" s="320"/>
+      <c r="D61" s="322"/>
       <c r="E61" s="322"/>
-      <c r="F61" s="320" t="s">
-        <v>141</v>
-      </c>
+      <c r="F61" s="320"/>
       <c r="G61" s="322"/>
-      <c r="H61" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H61" s="324"/>
       <c r="I61" s="294"/>
       <c r="J61" s="294"/>
       <c r="K61" s="294"/>
@@ -28631,24 +28583,14 @@
       <c r="Y61" s="294"/>
     </row>
     <row r="62" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="346" t="s">
-        <v>142</v>
-      </c>
+      <c r="A62" s="346"/>
       <c r="B62" s="322"/>
-      <c r="C62" s="320" t="s">
-        <v>143</v>
-      </c>
-      <c r="D62" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C62" s="320"/>
+      <c r="D62" s="322"/>
       <c r="E62" s="322"/>
-      <c r="F62" s="320" t="s">
-        <v>144</v>
-      </c>
+      <c r="F62" s="320"/>
       <c r="G62" s="322"/>
-      <c r="H62" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H62" s="324"/>
       <c r="I62" s="294"/>
       <c r="J62" s="294"/>
       <c r="K62" s="294"/>
@@ -28668,24 +28610,14 @@
       <c r="Y62" s="294"/>
     </row>
     <row r="63" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="347" t="s">
-        <v>145</v>
-      </c>
+      <c r="A63" s="347"/>
       <c r="B63" s="333"/>
-      <c r="C63" s="348" t="s">
-        <v>146</v>
-      </c>
-      <c r="D63" s="334" t="s">
-        <v>15</v>
-      </c>
+      <c r="C63" s="348"/>
+      <c r="D63" s="334"/>
       <c r="E63" s="333"/>
-      <c r="F63" s="348" t="s">
-        <v>147</v>
-      </c>
+      <c r="F63" s="348"/>
       <c r="G63" s="333"/>
-      <c r="H63" s="336" t="s">
-        <v>114</v>
-      </c>
+      <c r="H63" s="336"/>
       <c r="I63" s="294"/>
       <c r="J63" s="294"/>
       <c r="K63" s="294"/>
@@ -28705,24 +28637,14 @@
       <c r="Y63" s="294"/>
     </row>
     <row r="64" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="349" t="s">
-        <v>148</v>
-      </c>
+      <c r="A64" s="349"/>
       <c r="B64" s="340"/>
-      <c r="C64" s="350" t="s">
-        <v>149</v>
-      </c>
-      <c r="D64" s="341" t="s">
-        <v>15</v>
-      </c>
+      <c r="C64" s="350"/>
+      <c r="D64" s="341"/>
       <c r="E64" s="340"/>
-      <c r="F64" s="351" t="s">
-        <v>150</v>
-      </c>
+      <c r="F64" s="351"/>
       <c r="G64" s="340"/>
-      <c r="H64" s="343" t="s">
-        <v>104</v>
-      </c>
+      <c r="H64" s="343"/>
       <c r="I64" s="294"/>
       <c r="J64" s="294"/>
       <c r="K64" s="294"/>
@@ -28742,24 +28664,14 @@
       <c r="Y64" s="294"/>
     </row>
     <row r="65" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="346" t="s">
-        <v>151</v>
-      </c>
+      <c r="A65" s="346"/>
       <c r="B65" s="322"/>
-      <c r="C65" s="329" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C65" s="329"/>
+      <c r="D65" s="322"/>
       <c r="E65" s="322"/>
-      <c r="F65" s="320" t="s">
-        <v>153</v>
-      </c>
+      <c r="F65" s="320"/>
       <c r="G65" s="322"/>
-      <c r="H65" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H65" s="324"/>
       <c r="I65" s="294"/>
       <c r="J65" s="294"/>
       <c r="K65" s="294"/>
@@ -28779,24 +28691,14 @@
       <c r="Y65" s="294"/>
     </row>
     <row r="66" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="346" t="s">
-        <v>154</v>
-      </c>
+      <c r="A66" s="346"/>
       <c r="B66" s="322"/>
-      <c r="C66" s="320" t="s">
-        <v>155</v>
-      </c>
-      <c r="D66" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C66" s="320"/>
+      <c r="D66" s="322"/>
       <c r="E66" s="322"/>
-      <c r="F66" s="320" t="s">
-        <v>156</v>
-      </c>
+      <c r="F66" s="320"/>
       <c r="G66" s="322"/>
-      <c r="H66" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H66" s="324"/>
       <c r="I66" s="294"/>
       <c r="J66" s="294"/>
       <c r="K66" s="294"/>
@@ -28816,24 +28718,14 @@
       <c r="Y66" s="294"/>
     </row>
     <row r="67" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="346" t="s">
-        <v>157</v>
-      </c>
+      <c r="A67" s="346"/>
       <c r="B67" s="322"/>
-      <c r="C67" s="320" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C67" s="320"/>
+      <c r="D67" s="322"/>
       <c r="E67" s="322"/>
-      <c r="F67" s="320" t="s">
-        <v>159</v>
-      </c>
+      <c r="F67" s="320"/>
       <c r="G67" s="322"/>
-      <c r="H67" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H67" s="324"/>
       <c r="I67" s="294"/>
       <c r="J67" s="294"/>
       <c r="K67" s="294"/>
@@ -28853,24 +28745,14 @@
       <c r="Y67" s="294"/>
     </row>
     <row r="68" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="347" t="s">
-        <v>160</v>
-      </c>
+      <c r="A68" s="347"/>
       <c r="B68" s="333"/>
-      <c r="C68" s="348" t="s">
-        <v>161</v>
-      </c>
-      <c r="D68" s="334" t="s">
-        <v>15</v>
-      </c>
+      <c r="C68" s="348"/>
+      <c r="D68" s="334"/>
       <c r="E68" s="333"/>
-      <c r="F68" s="348" t="s">
-        <v>162</v>
-      </c>
+      <c r="F68" s="348"/>
       <c r="G68" s="333"/>
-      <c r="H68" s="336" t="s">
-        <v>114</v>
-      </c>
+      <c r="H68" s="336"/>
       <c r="I68" s="294"/>
       <c r="J68" s="294"/>
       <c r="K68" s="294"/>
@@ -28890,24 +28772,14 @@
       <c r="Y68" s="294"/>
     </row>
     <row r="69" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="352" t="s">
-        <v>163</v>
-      </c>
+      <c r="A69" s="352"/>
       <c r="B69" s="341"/>
-      <c r="C69" s="353" t="s">
-        <v>164</v>
-      </c>
-      <c r="D69" s="341" t="s">
-        <v>15</v>
-      </c>
+      <c r="C69" s="353"/>
+      <c r="D69" s="341"/>
       <c r="E69" s="341"/>
-      <c r="F69" s="353" t="s">
-        <v>165</v>
-      </c>
+      <c r="F69" s="353"/>
       <c r="G69" s="341"/>
-      <c r="H69" s="343" t="s">
-        <v>104</v>
-      </c>
+      <c r="H69" s="343"/>
       <c r="I69" s="294"/>
       <c r="J69" s="294"/>
       <c r="K69" s="294"/>
@@ -28927,24 +28799,14 @@
       <c r="Y69" s="294"/>
     </row>
     <row r="70" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="346" t="s">
-        <v>166</v>
-      </c>
+      <c r="A70" s="346"/>
       <c r="B70" s="322"/>
-      <c r="C70" s="320" t="s">
-        <v>167</v>
-      </c>
-      <c r="D70" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C70" s="320"/>
+      <c r="D70" s="322"/>
       <c r="E70" s="322"/>
-      <c r="F70" s="320" t="s">
-        <v>168</v>
-      </c>
+      <c r="F70" s="320"/>
       <c r="G70" s="322"/>
-      <c r="H70" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H70" s="324"/>
       <c r="I70" s="294"/>
       <c r="J70" s="294"/>
       <c r="K70" s="294"/>
@@ -28964,24 +28826,14 @@
       <c r="Y70" s="294"/>
     </row>
     <row r="71" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="346" t="s">
-        <v>169</v>
-      </c>
+      <c r="A71" s="346"/>
       <c r="B71" s="322"/>
-      <c r="C71" s="360" t="s">
-        <v>170</v>
-      </c>
-      <c r="D71" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C71" s="360"/>
+      <c r="D71" s="322"/>
       <c r="E71" s="321"/>
-      <c r="F71" s="360" t="s">
-        <v>171</v>
-      </c>
+      <c r="F71" s="360"/>
       <c r="G71" s="321"/>
-      <c r="H71" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H71" s="324"/>
       <c r="I71" s="294"/>
       <c r="J71" s="294"/>
       <c r="K71" s="294"/>
@@ -29001,24 +28853,14 @@
       <c r="Y71" s="294"/>
     </row>
     <row r="72" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="346" t="s">
-        <v>172</v>
-      </c>
+      <c r="A72" s="346"/>
       <c r="B72" s="322"/>
-      <c r="C72" s="360" t="s">
-        <v>173</v>
-      </c>
-      <c r="D72" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C72" s="360"/>
+      <c r="D72" s="322"/>
       <c r="E72" s="321"/>
-      <c r="F72" s="360" t="s">
-        <v>174</v>
-      </c>
+      <c r="F72" s="360"/>
       <c r="G72" s="321"/>
-      <c r="H72" s="324" t="s">
-        <v>114</v>
-      </c>
+      <c r="H72" s="324"/>
       <c r="I72" s="294"/>
       <c r="J72" s="294"/>
       <c r="K72" s="294"/>
@@ -29038,24 +28880,14 @@
       <c r="Y72" s="294"/>
     </row>
     <row r="73" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="347" t="s">
-        <v>175</v>
-      </c>
+      <c r="A73" s="347"/>
       <c r="B73" s="333"/>
-      <c r="C73" s="348" t="s">
-        <v>176</v>
-      </c>
-      <c r="D73" s="333" t="s">
-        <v>15</v>
-      </c>
+      <c r="C73" s="348"/>
+      <c r="D73" s="333"/>
       <c r="E73" s="333"/>
-      <c r="F73" s="348" t="s">
-        <v>177</v>
-      </c>
+      <c r="F73" s="348"/>
       <c r="G73" s="333"/>
-      <c r="H73" s="336" t="s">
-        <v>114</v>
-      </c>
+      <c r="H73" s="336"/>
       <c r="I73" s="294"/>
       <c r="J73" s="294"/>
       <c r="K73" s="294"/>
@@ -29075,24 +28907,14 @@
       <c r="Y73" s="294"/>
     </row>
     <row r="74" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="349" t="s">
-        <v>178</v>
-      </c>
+      <c r="A74" s="349"/>
       <c r="B74" s="340"/>
-      <c r="C74" s="351" t="s">
-        <v>179</v>
-      </c>
-      <c r="D74" s="341" t="s">
-        <v>15</v>
-      </c>
+      <c r="C74" s="351"/>
+      <c r="D74" s="341"/>
       <c r="E74" s="340"/>
-      <c r="F74" s="351" t="s">
-        <v>180</v>
-      </c>
+      <c r="F74" s="351"/>
       <c r="G74" s="340"/>
-      <c r="H74" s="343" t="s">
-        <v>104</v>
-      </c>
+      <c r="H74" s="343"/>
       <c r="I74" s="294"/>
       <c r="J74" s="294"/>
       <c r="K74" s="294"/>
@@ -29112,24 +28934,14 @@
       <c r="Y74" s="294"/>
     </row>
     <row r="75" ht="15.95" customHeight="1" spans="1:25" s="294" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="346" t="s">
-        <v>181</v>
-      </c>
+      <c r="A75" s="346"/>
       <c r="B75" s="322"/>
-      <c r="C75" s="360" t="s">
-        <v>182</v>
-      </c>
-      <c r="D75" s="322" t="s">
-        <v>15</v>
-      </c>
+      <c r="C75" s="360"/>
+      <c r="D75" s="322"/>
       <c r="E75" s="321"/>
-      <c r="F75" s="360" t="s">
-        <v>183</v>
-      </c>
+      <c r="F75" s="360"/>
       <c r="G75" s="321"/>
-      <c r="H75" s="324" t="s">
-        <v>104</v>
-      </c>
+      <c r="H75" s="324"/>
       <c r="I75" s="294"/>
       <c r="J75" s="294"/>
       <c r="K75" s="294"/>
